--- a/final/Siruk-hx-303-prices-dog.xlsx
+++ b/final/Siruk-hx-303-prices-dog.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3550</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2800</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="27">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4050</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="50">

--- a/final/Siruk-hx-303-prices-dog.xlsx
+++ b/final/Siruk-hx-303-prices-dog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,6 +1898,106 @@
         <v>8000</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Հյուրասիրություն շների Bony Mix` գունավոր ոսկորիկներ  կգ</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Soft Snack Bony Mix XXL — 1,800 g</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>00107</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Պեչենի շն.` գունավոր խառը ոսկորիկներ, մեծ կգ</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cookie Bones — 1.3 kg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>00108</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Պեչենի շն.` գունավոր մանր կենդանիներ, Farmies   կգ</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cookie Farmies — 1.3 kg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>00109</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Թխվածքաբլիթներ շն.` գառան մսով, կգ</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cookie Giants with Lamb — 1.25 kg</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>00110</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Պեչենի շն.` գունավոր օղակներ Vegan Loops,  կգ</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cookie Snack Loops — 1.3 kg</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>00111</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/final/Siruk-hx-303-prices-dog.xlsx
+++ b/final/Siruk-hx-303-prices-dog.xlsx
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4100</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4100</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3700</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5100</v>
+        <v>6000</v>
       </c>
     </row>
   </sheetData>

--- a/final/Siruk-hx-303-prices-dog.xlsx
+++ b/final/Siruk-hx-303-prices-dog.xlsx
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5000</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5000</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5200</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6000</v>
+        <v>5100</v>
       </c>
     </row>
   </sheetData>

--- a/final/Siruk-hx-303-prices-dog.xlsx
+++ b/final/Siruk-hx-303-prices-dog.xlsx
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3700</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5100</v>
+        <v>6600</v>
       </c>
     </row>
   </sheetData>

--- a/final/Siruk-hx-303-prices-dog.xlsx
+++ b/final/Siruk-hx-303-prices-dog.xlsx
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="76">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5500</v>
+        <v>550</v>
       </c>
     </row>
     <row r="77">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5500</v>
+        <v>550</v>
       </c>
     </row>
     <row r="78">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5700</v>
+        <v>570</v>
       </c>
     </row>
     <row r="79">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6600</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
